--- a/clients/encore/test_cases_xlsx/encore_test_cases.xlsx
+++ b/clients/encore/test_cases_xlsx/encore_test_cases.xlsx
@@ -29,9 +29,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7177" uniqueCount="2786">
-  <si>
-    <t>Encore Test Case Workbook — generated on 2026-06-09 06:19</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7177" uniqueCount="2788">
+  <si>
+    <t>Encore Test Case Workbook — generated on 2026-06-09 06:50</t>
   </si>
   <si>
     <t>Workbook version: encore_test_cases.xlsx</t>
@@ -157,7 +157,7 @@
     <t>16.7%</t>
   </si>
   <si>
-    <t>17.4%</t>
+    <t>17.8%</t>
   </si>
   <si>
     <t>locations_management_history</t>
@@ -184,7 +184,7 @@
     <t>locations_shared_setup_location</t>
   </si>
   <si>
-    <t>84.1%</t>
+    <t>79.5%</t>
   </si>
   <si>
     <t>TC ID</t>
@@ -6229,6 +6229,9 @@
     <t>Save button stays disabled when LDW Percentage = -10 (out of range; min=0). User must restore a valid value before Save enables. Old-site baseline behavior (form-validity wiring) restored on new site</t>
   </si>
   <si>
+    <t>the application disables Save on a maximum-value violation, so the invalid value is never saved</t>
+  </si>
+  <si>
     <t>TC-LOC-LI-036</t>
   </si>
   <si>
@@ -7496,7 +7499,7 @@
     <t>Automated: 19 / Pending: 91</t>
   </si>
   <si>
-    <t>Pass:19 Fail:0 Skipped:0 Blocked:5</t>
+    <t>Pass:19 Fail:0 Skipped:0 Blocked:7</t>
   </si>
   <si>
     <t>TC-LOC-MGH-001</t>
@@ -9827,6 +9830,9 @@
     <t>Reverting to original state removes unsaved changes, Save disables</t>
   </si>
   <si>
+    <t>Blocked — reverting Shares Inventory on an added row to its original state leaves the form marked as changed, so Save stays enabled even though there is no net change. Pending an application fix</t>
+  </si>
+  <si>
     <t>TC-LOC-SSL-008</t>
   </si>
   <si>
@@ -10249,6 +10255,9 @@
     <t>Cleanup after test: (restore to baseline): delete all non-self rows + Save until only the self-row remains; reload + verify count = 1</t>
   </si>
   <si>
+    <t>Blocked — the per-row Delete control intermittently stops responding after a row is added, saved and the page reloaded, so the cleanup step cannot complete reliably. Pending an application fix</t>
+  </si>
+  <si>
     <t>TC-LOC-SSL-031</t>
   </si>
   <si>
@@ -10270,9 +10279,6 @@
     <t>Cleanup after test: -&gt; ensureCleanSSLTable</t>
   </si>
   <si>
-    <t>Blocked — the per-row Delete control intermittently stops responding after a row is added, saved and the page reloaded, so the cleanup step cannot complete reliably. Pending an application fix</t>
-  </si>
-  <si>
     <t>TC-LOC-SSL-032</t>
   </si>
   <si>
@@ -10421,7 +10427,7 @@
     <t>Automated: 44 / Pending: 0</t>
   </si>
   <si>
-    <t>Pass:37 Fail:0 Skipped:0 Blocked:7</t>
+    <t>Pass:35 Fail:0 Skipped:0 Blocked:9</t>
   </si>
 </sst>
 </file>
@@ -11418,7 +11424,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I18" t="s">
         <v>41</v>
@@ -11561,7 +11567,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -11570,7 +11576,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I22" t="s">
         <v>51</v>
@@ -17536,18 +17542,18 @@
         <v>5</v>
       </c>
       <c r="J39" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="K39" t="s">
-        <v>70</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B40" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="C40" t="s">
         <v>462</v>
@@ -17559,10 +17565,10 @@
         <v>1588</v>
       </c>
       <c r="F40" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G40" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="H40" t="s">
         <v>70</v>
@@ -17579,10 +17585,10 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B41" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="C41" t="s">
         <v>462</v>
@@ -17594,10 +17600,10 @@
         <v>1588</v>
       </c>
       <c r="F41" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="G41" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="H41" t="s">
         <v>70</v>
@@ -17606,18 +17612,18 @@
         <v>5</v>
       </c>
       <c r="J41" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="K41" t="s">
-        <v>70</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B42" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="C42" t="s">
         <v>462</v>
@@ -17629,10 +17635,10 @@
         <v>1541</v>
       </c>
       <c r="F42" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="G42" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="H42" t="s">
         <v>70</v>
@@ -17649,10 +17655,10 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B43" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="C43" t="s">
         <v>462</v>
@@ -17664,10 +17670,10 @@
         <v>1541</v>
       </c>
       <c r="F43" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="G43" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="H43" t="s">
         <v>70</v>
@@ -17684,10 +17690,10 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B44" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="C44" t="s">
         <v>462</v>
@@ -17699,10 +17705,10 @@
         <v>1541</v>
       </c>
       <c r="F44" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="G44" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="H44" t="s">
         <v>70</v>
@@ -17719,10 +17725,10 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B45" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="C45" t="s">
         <v>462</v>
@@ -17734,10 +17740,10 @@
         <v>1541</v>
       </c>
       <c r="F45" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="G45" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H45" t="s">
         <v>70</v>
@@ -17754,10 +17760,10 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B46" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="C46" t="s">
         <v>462</v>
@@ -17769,10 +17775,10 @@
         <v>1541</v>
       </c>
       <c r="F46" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="G46" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H46" t="s">
         <v>70</v>
@@ -17789,10 +17795,10 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B47" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="C47" t="s">
         <v>462</v>
@@ -17804,10 +17810,10 @@
         <v>1541</v>
       </c>
       <c r="F47" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="G47" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="H47" t="s">
         <v>70</v>
@@ -17824,10 +17830,10 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B48" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="C48" t="s">
         <v>462</v>
@@ -17839,10 +17845,10 @@
         <v>1541</v>
       </c>
       <c r="F48" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="G48" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="H48" t="s">
         <v>70</v>
@@ -17859,10 +17865,10 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B49" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="C49" t="s">
         <v>462</v>
@@ -17874,10 +17880,10 @@
         <v>1541</v>
       </c>
       <c r="F49" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="G49" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="H49" t="s">
         <v>70</v>
@@ -17894,10 +17900,10 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B50" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="C50" t="s">
         <v>462</v>
@@ -17906,16 +17912,16 @@
         <v>1540</v>
       </c>
       <c r="E50" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="F50" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="G50" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="H50" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="I50" t="s">
         <v>5</v>
@@ -17929,10 +17935,10 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B51" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="C51" t="s">
         <v>462</v>
@@ -17944,13 +17950,13 @@
         <v>1541</v>
       </c>
       <c r="F51" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="G51" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="H51" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="I51" t="s">
         <v>5</v>
@@ -17964,10 +17970,10 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B52" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="C52" t="s">
         <v>462</v>
@@ -17976,16 +17982,16 @@
         <v>1540</v>
       </c>
       <c r="E52" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="F52" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="G52" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="H52" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="I52" t="s">
         <v>5</v>
@@ -17999,10 +18005,10 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="B53" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="C53" t="s">
         <v>462</v>
@@ -18014,10 +18020,10 @@
         <v>1541</v>
       </c>
       <c r="F53" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="G53" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="H53" t="s">
         <v>70</v>
@@ -18034,10 +18040,10 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B54" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="C54" t="s">
         <v>462</v>
@@ -18049,10 +18055,10 @@
         <v>1541</v>
       </c>
       <c r="F54" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="G54" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="H54" t="s">
         <v>70</v>
@@ -18069,10 +18075,10 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B55" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="C55" t="s">
         <v>462</v>
@@ -18084,10 +18090,10 @@
         <v>1541</v>
       </c>
       <c r="F55" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="G55" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="H55" t="s">
         <v>70</v>
@@ -18104,10 +18110,10 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B56" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="C56" t="s">
         <v>462</v>
@@ -18119,13 +18125,13 @@
         <v>1541</v>
       </c>
       <c r="F56" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="G56" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="H56" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="I56" t="s">
         <v>5</v>
@@ -18139,10 +18145,10 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="B57" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="C57" t="s">
         <v>462</v>
@@ -18154,10 +18160,10 @@
         <v>1541</v>
       </c>
       <c r="F57" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="G57" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="H57" t="s">
         <v>70</v>
@@ -18174,10 +18180,10 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="B58" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="C58" t="s">
         <v>462</v>
@@ -18189,10 +18195,10 @@
         <v>1541</v>
       </c>
       <c r="F58" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="G58" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="H58" t="s">
         <v>70</v>
@@ -18204,15 +18210,15 @@
         <v>70</v>
       </c>
       <c r="K58" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B59" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="C59" t="s">
         <v>462</v>
@@ -18224,13 +18230,13 @@
         <v>1541</v>
       </c>
       <c r="F59" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="G59" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="H59" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="I59" t="s">
         <v>5</v>
@@ -18244,10 +18250,10 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B60" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="C60" t="s">
         <v>462</v>
@@ -18256,13 +18262,13 @@
         <v>1540</v>
       </c>
       <c r="E60" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="F60" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="G60" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="H60" t="s">
         <v>70</v>
@@ -18279,10 +18285,10 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B61" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="C61" t="s">
         <v>462</v>
@@ -18294,10 +18300,10 @@
         <v>1588</v>
       </c>
       <c r="F61" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="G61" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="H61" t="s">
         <v>70</v>
@@ -18309,15 +18315,15 @@
         <v>70</v>
       </c>
       <c r="K61" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B62" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="C62" t="s">
         <v>462</v>
@@ -18329,10 +18335,10 @@
         <v>1541</v>
       </c>
       <c r="F62" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="G62" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="H62" t="s">
         <v>70</v>
@@ -18349,10 +18355,10 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B63" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="C63" t="s">
         <v>462</v>
@@ -18361,16 +18367,16 @@
         <v>1540</v>
       </c>
       <c r="E63" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="F63" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="G63" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="H63" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="I63" t="s">
         <v>5</v>
@@ -18384,10 +18390,10 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B64" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="C64" t="s">
         <v>462</v>
@@ -18396,16 +18402,16 @@
         <v>1540</v>
       </c>
       <c r="E64" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="F64" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="G64" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="H64" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="I64" t="s">
         <v>5</v>
@@ -18419,10 +18425,10 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B65" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="C65" t="s">
         <v>462</v>
@@ -18434,10 +18440,10 @@
         <v>1541</v>
       </c>
       <c r="F65" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="G65" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="H65" t="s">
         <v>70</v>
@@ -18454,10 +18460,10 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B66" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="C66" t="s">
         <v>462</v>
@@ -18469,10 +18475,10 @@
         <v>1541</v>
       </c>
       <c r="F66" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="G66" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="H66" t="s">
         <v>70</v>
@@ -18484,15 +18490,15 @@
         <v>9</v>
       </c>
       <c r="K66" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="B67" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="C67" t="s">
         <v>462</v>
@@ -18504,10 +18510,10 @@
         <v>1541</v>
       </c>
       <c r="F67" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="G67" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="H67" t="s">
         <v>70</v>
@@ -18524,10 +18530,10 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B68" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="C68" t="s">
         <v>462</v>
@@ -18539,13 +18545,13 @@
         <v>1541</v>
       </c>
       <c r="F68" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="G68" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="H68" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="I68" t="s">
         <v>4</v>
@@ -18559,10 +18565,10 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B69" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="C69" t="s">
         <v>462</v>
@@ -18574,13 +18580,13 @@
         <v>1541</v>
       </c>
       <c r="F69" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="G69" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="H69" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="I69" t="s">
         <v>4</v>
@@ -18594,10 +18600,10 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B70" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="C70" t="s">
         <v>462</v>
@@ -18609,13 +18615,13 @@
         <v>1541</v>
       </c>
       <c r="F70" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="G70" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="H70" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="I70" t="s">
         <v>4</v>
@@ -18629,10 +18635,10 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B71" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="C71" t="s">
         <v>462</v>
@@ -18644,13 +18650,13 @@
         <v>1541</v>
       </c>
       <c r="F71" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="G71" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="H71" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="I71" t="s">
         <v>4</v>
@@ -18664,10 +18670,10 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="B72" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="C72" t="s">
         <v>462</v>
@@ -18679,13 +18685,13 @@
         <v>1541</v>
       </c>
       <c r="F72" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="G72" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="H72" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="I72" t="s">
         <v>4</v>
@@ -18699,10 +18705,10 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B73" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="C73" t="s">
         <v>462</v>
@@ -18714,13 +18720,13 @@
         <v>1541</v>
       </c>
       <c r="F73" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="G73" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="H73" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="I73" t="s">
         <v>4</v>
@@ -18734,10 +18740,10 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B74" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="C74" t="s">
         <v>462</v>
@@ -18749,13 +18755,13 @@
         <v>1541</v>
       </c>
       <c r="F74" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="G74" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="H74" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="I74" t="s">
         <v>4</v>
@@ -18769,10 +18775,10 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B75" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="C75" t="s">
         <v>462</v>
@@ -18784,13 +18790,13 @@
         <v>1541</v>
       </c>
       <c r="F75" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="G75" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="H75" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="I75" t="s">
         <v>4</v>
@@ -18804,10 +18810,10 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B76" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="C76" t="s">
         <v>462</v>
@@ -18819,13 +18825,13 @@
         <v>1541</v>
       </c>
       <c r="F76" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="G76" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="H76" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="I76" t="s">
         <v>4</v>
@@ -18839,10 +18845,10 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B77" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="C77" t="s">
         <v>462</v>
@@ -18854,13 +18860,13 @@
         <v>1541</v>
       </c>
       <c r="F77" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="G77" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="H77" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="I77" t="s">
         <v>4</v>
@@ -18874,10 +18880,10 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B78" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="C78" t="s">
         <v>462</v>
@@ -18889,13 +18895,13 @@
         <v>1693</v>
       </c>
       <c r="F78" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="G78" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="H78" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="I78" t="s">
         <v>5</v>
@@ -18904,15 +18910,15 @@
         <v>9</v>
       </c>
       <c r="K78" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="B79" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="C79" t="s">
         <v>462</v>
@@ -18924,13 +18930,13 @@
         <v>1541</v>
       </c>
       <c r="F79" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="G79" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="H79" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="I79" t="s">
         <v>5</v>
@@ -18939,15 +18945,15 @@
         <v>9</v>
       </c>
       <c r="K79" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="B80" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="C80" t="s">
         <v>462</v>
@@ -18959,13 +18965,13 @@
         <v>1541</v>
       </c>
       <c r="F80" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="G80" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="H80" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="I80" t="s">
         <v>5</v>
@@ -18979,10 +18985,10 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="B81" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="C81" t="s">
         <v>462</v>
@@ -18994,10 +19000,10 @@
         <v>1541</v>
       </c>
       <c r="F81" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="G81" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="H81" t="s">
         <v>70</v>
@@ -19014,10 +19020,10 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B82" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="C82" t="s">
         <v>462</v>
@@ -19029,10 +19035,10 @@
         <v>1541</v>
       </c>
       <c r="F82" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G82" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="H82" t="s">
         <v>70</v>
@@ -19049,10 +19055,10 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B83" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="C83" t="s">
         <v>462</v>
@@ -19064,10 +19070,10 @@
         <v>1541</v>
       </c>
       <c r="F83" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="G83" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="H83" t="s">
         <v>70</v>
@@ -19084,10 +19090,10 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B84" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="C84" t="s">
         <v>462</v>
@@ -19099,10 +19105,10 @@
         <v>1541</v>
       </c>
       <c r="F84" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="G84" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="H84" t="s">
         <v>70</v>
@@ -19119,10 +19125,10 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B85" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="C85" t="s">
         <v>462</v>
@@ -19134,10 +19140,10 @@
         <v>1541</v>
       </c>
       <c r="F85" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="G85" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="H85" t="s">
         <v>70</v>
@@ -19154,10 +19160,10 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B86" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="C86" t="s">
         <v>462</v>
@@ -19169,10 +19175,10 @@
         <v>1541</v>
       </c>
       <c r="F86" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="G86" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="H86" t="s">
         <v>70</v>
@@ -19189,10 +19195,10 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="B87" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="C87" t="s">
         <v>462</v>
@@ -19204,10 +19210,10 @@
         <v>1541</v>
       </c>
       <c r="F87" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="G87" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="H87" t="s">
         <v>70</v>
@@ -19224,10 +19230,10 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B88" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="C88" t="s">
         <v>462</v>
@@ -19239,10 +19245,10 @@
         <v>1541</v>
       </c>
       <c r="F88" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="G88" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="H88" t="s">
         <v>70</v>
@@ -19259,10 +19265,10 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B89" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="C89" t="s">
         <v>462</v>
@@ -19274,10 +19280,10 @@
         <v>1541</v>
       </c>
       <c r="F89" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="G89" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="H89" t="s">
         <v>70</v>
@@ -19294,10 +19300,10 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B90" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="C90" t="s">
         <v>462</v>
@@ -19309,10 +19315,10 @@
         <v>1541</v>
       </c>
       <c r="F90" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="G90" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="H90" t="s">
         <v>70</v>
@@ -19329,10 +19335,10 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="B91" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="C91" t="s">
         <v>462</v>
@@ -19344,10 +19350,10 @@
         <v>1541</v>
       </c>
       <c r="F91" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="G91" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="H91" t="s">
         <v>70</v>
@@ -19364,10 +19370,10 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="B92" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="C92" t="s">
         <v>462</v>
@@ -19379,10 +19385,10 @@
         <v>1541</v>
       </c>
       <c r="F92" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="G92" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="H92" t="s">
         <v>70</v>
@@ -19399,10 +19405,10 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="B93" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="C93" t="s">
         <v>462</v>
@@ -19414,10 +19420,10 @@
         <v>1541</v>
       </c>
       <c r="F93" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="G93" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="H93" t="s">
         <v>70</v>
@@ -19434,10 +19440,10 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="B94" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="C94" t="s">
         <v>462</v>
@@ -19449,10 +19455,10 @@
         <v>1541</v>
       </c>
       <c r="F94" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G94" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="H94" t="s">
         <v>70</v>
@@ -19469,10 +19475,10 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="B95" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="C95" t="s">
         <v>462</v>
@@ -19484,10 +19490,10 @@
         <v>1541</v>
       </c>
       <c r="F95" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="G95" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="H95" t="s">
         <v>70</v>
@@ -19504,10 +19510,10 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="B96" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="C96" t="s">
         <v>462</v>
@@ -19519,10 +19525,10 @@
         <v>1541</v>
       </c>
       <c r="F96" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="G96" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="H96" t="s">
         <v>70</v>
@@ -19539,10 +19545,10 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="B97" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="C97" t="s">
         <v>462</v>
@@ -19554,10 +19560,10 @@
         <v>1541</v>
       </c>
       <c r="F97" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="G97" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="H97" t="s">
         <v>70</v>
@@ -19574,10 +19580,10 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="B98" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="C98" t="s">
         <v>462</v>
@@ -19589,10 +19595,10 @@
         <v>1541</v>
       </c>
       <c r="F98" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="G98" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="H98" t="s">
         <v>70</v>
@@ -19609,10 +19615,10 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="B99" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="C99" t="s">
         <v>462</v>
@@ -19624,10 +19630,10 @@
         <v>1541</v>
       </c>
       <c r="F99" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="G99" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H99" t="s">
         <v>70</v>
@@ -19644,10 +19650,10 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="B100" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="C100" t="s">
         <v>462</v>
@@ -19659,10 +19665,10 @@
         <v>1541</v>
       </c>
       <c r="F100" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="G100" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="H100" t="s">
         <v>70</v>
@@ -19679,10 +19685,10 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="B101" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="C101" t="s">
         <v>462</v>
@@ -19694,10 +19700,10 @@
         <v>1541</v>
       </c>
       <c r="F101" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="G101" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="H101" t="s">
         <v>70</v>
@@ -19714,10 +19720,10 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="B102" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="C102" t="s">
         <v>462</v>
@@ -19729,10 +19735,10 @@
         <v>1541</v>
       </c>
       <c r="F102" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="G102" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="H102" t="s">
         <v>70</v>
@@ -19749,10 +19755,10 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="B103" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="C103" t="s">
         <v>462</v>
@@ -19764,10 +19770,10 @@
         <v>1541</v>
       </c>
       <c r="F103" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="G103" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="H103" t="s">
         <v>70</v>
@@ -19784,10 +19790,10 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B104" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="C104" t="s">
         <v>462</v>
@@ -19799,10 +19805,10 @@
         <v>1541</v>
       </c>
       <c r="F104" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="G104" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="H104" t="s">
         <v>70</v>
@@ -19819,10 +19825,10 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B105" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="C105" t="s">
         <v>462</v>
@@ -19831,13 +19837,13 @@
         <v>1540</v>
       </c>
       <c r="E105" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="F105" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="G105" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H105" t="s">
         <v>70</v>
@@ -19854,10 +19860,10 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="B106" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="C106" t="s">
         <v>462</v>
@@ -19866,13 +19872,13 @@
         <v>1540</v>
       </c>
       <c r="E106" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="F106" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="G106" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="H106" t="s">
         <v>70</v>
@@ -19889,10 +19895,10 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B107" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="C107" t="s">
         <v>462</v>
@@ -19901,13 +19907,13 @@
         <v>1540</v>
       </c>
       <c r="E107" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="F107" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="G107" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H107" t="s">
         <v>70</v>
@@ -19924,10 +19930,10 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B108" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="C108" t="s">
         <v>462</v>
@@ -19936,13 +19942,13 @@
         <v>1540</v>
       </c>
       <c r="E108" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="F108" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="G108" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="H108" t="s">
         <v>70</v>
@@ -19959,10 +19965,10 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B109" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="C109" t="s">
         <v>462</v>
@@ -19971,13 +19977,13 @@
         <v>1540</v>
       </c>
       <c r="E109" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="F109" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="G109" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H109" t="s">
         <v>70</v>
@@ -19994,10 +20000,10 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B110" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="C110" t="s">
         <v>462</v>
@@ -20006,13 +20012,13 @@
         <v>1540</v>
       </c>
       <c r="E110" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="F110" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="G110" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H110" t="s">
         <v>70</v>
@@ -20029,10 +20035,10 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B111" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="C111" t="s">
         <v>462</v>
@@ -20041,19 +20047,19 @@
         <v>1540</v>
       </c>
       <c r="E111" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="F111" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="G111" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H111" t="s">
         <v>70</v>
       </c>
       <c r="I111" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="J111" t="s">
         <v>70</v>
@@ -20064,10 +20070,10 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B112" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C112" t="s">
         <v>462</v>
@@ -20076,19 +20082,19 @@
         <v>1540</v>
       </c>
       <c r="E112" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="F112" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="G112" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H112" t="s">
         <v>70</v>
       </c>
       <c r="I112" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="J112" t="s">
         <v>70</v>
@@ -20099,10 +20105,10 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B113" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C113" t="s">
         <v>462</v>
@@ -20111,19 +20117,19 @@
         <v>1540</v>
       </c>
       <c r="E113" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F113" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="G113" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H113" t="s">
         <v>70</v>
       </c>
       <c r="I113" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="J113" t="s">
         <v>70</v>
@@ -20134,10 +20140,10 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B114" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C114" t="s">
         <v>462</v>
@@ -20146,19 +20152,19 @@
         <v>1540</v>
       </c>
       <c r="E114" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F114" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G114" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H114" t="s">
         <v>70</v>
       </c>
       <c r="I114" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="J114" t="s">
         <v>70</v>
@@ -20169,10 +20175,10 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B115" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C115" t="s">
         <v>462</v>
@@ -20184,13 +20190,13 @@
         <v>1541</v>
       </c>
       <c r="F115" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G115" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="H115" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="I115" t="s">
         <v>4</v>
@@ -20207,7 +20213,7 @@
         <v>144</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>70</v>
@@ -20228,10 +20234,10 @@
         <v>70</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="J117" s="6" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="K117" s="6" t="s">
         <v>148</v>
@@ -20296,25 +20302,25 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B2" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="C2" t="s">
         <v>462</v>
       </c>
       <c r="D2" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E2" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="F2" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="G2" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="H2" t="s">
         <v>70</v>
@@ -20331,25 +20337,25 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B3" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="C3" t="s">
         <v>462</v>
       </c>
       <c r="D3" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E3" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="F3" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="G3" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="H3" t="s">
         <v>70</v>
@@ -20366,25 +20372,25 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B4" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="C4" t="s">
         <v>462</v>
       </c>
       <c r="D4" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E4" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="F4" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="G4" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="H4" t="s">
         <v>70</v>
@@ -20401,25 +20407,25 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="B5" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="C5" t="s">
         <v>462</v>
       </c>
       <c r="D5" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E5" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="F5" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="G5" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="H5" t="s">
         <v>70</v>
@@ -20436,28 +20442,28 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B6" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="C6" t="s">
         <v>462</v>
       </c>
       <c r="D6" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E6" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="F6" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="G6" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="H6" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="I6" t="s">
         <v>4</v>
@@ -20471,25 +20477,25 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="B7" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="C7" t="s">
         <v>462</v>
       </c>
       <c r="D7" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E7" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="F7" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="G7" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="H7" t="s">
         <v>70</v>
@@ -20506,25 +20512,25 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="B8" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="C8" t="s">
         <v>462</v>
       </c>
       <c r="D8" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E8" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="F8" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G8" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="H8" t="s">
         <v>70</v>
@@ -20541,25 +20547,25 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="B9" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="C9" t="s">
         <v>462</v>
       </c>
       <c r="D9" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E9" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="F9" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="G9" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="H9" t="s">
         <v>70</v>
@@ -20576,25 +20582,25 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="B10" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="C10" t="s">
         <v>462</v>
       </c>
       <c r="D10" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E10" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="F10" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="G10" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="H10" t="s">
         <v>70</v>
@@ -20611,25 +20617,25 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="B11" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="C11" t="s">
         <v>462</v>
       </c>
       <c r="D11" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E11" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="F11" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="G11" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="H11" t="s">
         <v>70</v>
@@ -20646,25 +20652,25 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="B12" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="C12" t="s">
         <v>462</v>
       </c>
       <c r="D12" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E12" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="F12" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="G12" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="H12" t="s">
         <v>70</v>
@@ -20681,25 +20687,25 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="B13" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="C13" t="s">
         <v>462</v>
       </c>
       <c r="D13" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E13" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="F13" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="G13" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="H13" t="s">
         <v>70</v>
@@ -20716,25 +20722,25 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="B14" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="C14" t="s">
         <v>462</v>
       </c>
       <c r="D14" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E14" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="F14" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="G14" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="H14" t="s">
         <v>70</v>
@@ -20751,25 +20757,25 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="B15" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="C15" t="s">
         <v>462</v>
       </c>
       <c r="D15" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E15" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="F15" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="G15" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="H15" t="s">
         <v>70</v>
@@ -20786,25 +20792,25 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="B16" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="C16" t="s">
         <v>462</v>
       </c>
       <c r="D16" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E16" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="F16" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="G16" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="H16" t="s">
         <v>70</v>
@@ -20821,25 +20827,25 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B17" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="C17" t="s">
         <v>462</v>
       </c>
       <c r="D17" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E17" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="F17" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G17" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="H17" t="s">
         <v>70</v>
@@ -20856,25 +20862,25 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="B18" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="C18" t="s">
         <v>462</v>
       </c>
       <c r="D18" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E18" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="F18" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="G18" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="H18" t="s">
         <v>70</v>
@@ -20891,25 +20897,25 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="B19" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="C19" t="s">
         <v>462</v>
       </c>
       <c r="D19" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E19" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="F19" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="G19" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="H19" t="s">
         <v>70</v>
@@ -20926,25 +20932,25 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="B20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="C20" t="s">
         <v>462</v>
       </c>
       <c r="D20" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E20" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="F20" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="G20" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="H20" t="s">
         <v>70</v>
@@ -20961,25 +20967,25 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="B21" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="C21" t="s">
         <v>462</v>
       </c>
       <c r="D21" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E21" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="F21" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="G21" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="H21" t="s">
         <v>70</v>
@@ -20996,25 +21002,25 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="B22" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="C22" t="s">
         <v>462</v>
       </c>
       <c r="D22" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E22" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="F22" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="G22" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="H22" t="s">
         <v>70</v>
@@ -21031,25 +21037,25 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="B23" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="C23" t="s">
         <v>462</v>
       </c>
       <c r="D23" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E23" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="F23" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="G23" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="H23" t="s">
         <v>70</v>
@@ -21066,25 +21072,25 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="B24" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="C24" t="s">
         <v>462</v>
       </c>
       <c r="D24" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E24" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="F24" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="G24" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="H24" t="s">
         <v>70</v>
@@ -21101,25 +21107,25 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="B25" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="C25" t="s">
         <v>462</v>
       </c>
       <c r="D25" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E25" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="F25" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="G25" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="H25" t="s">
         <v>70</v>
@@ -21136,25 +21142,25 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="B26" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="C26" t="s">
         <v>462</v>
       </c>
       <c r="D26" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E26" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="F26" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="G26" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="H26" t="s">
         <v>70</v>
@@ -21174,7 +21180,7 @@
         <v>144</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>70</v>
@@ -21262,28 +21268,28 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="B2" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="C2" t="s">
         <v>462</v>
       </c>
       <c r="D2" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E2" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F2" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="G2" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="H2" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="I2" t="s">
         <v>4</v>
@@ -21297,28 +21303,28 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="B3" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="C3" t="s">
         <v>462</v>
       </c>
       <c r="D3" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E3" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F3" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="G3" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="H3" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="I3" t="s">
         <v>4</v>
@@ -21332,28 +21338,28 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="B4" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="C4" t="s">
         <v>462</v>
       </c>
       <c r="D4" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E4" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F4" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="G4" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="H4" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="I4" t="s">
         <v>4</v>
@@ -21367,28 +21373,28 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="B5" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="C5" t="s">
         <v>462</v>
       </c>
       <c r="D5" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E5" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F5" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="G5" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="H5" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="I5" t="s">
         <v>4</v>
@@ -21402,28 +21408,28 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="B6" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="C6" t="s">
         <v>462</v>
       </c>
       <c r="D6" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E6" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F6" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="G6" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="H6" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="I6" t="s">
         <v>4</v>
@@ -21437,28 +21443,28 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="B7" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="C7" t="s">
         <v>462</v>
       </c>
       <c r="D7" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E7" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F7" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="G7" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="H7" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="I7" t="s">
         <v>4</v>
@@ -21472,28 +21478,28 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="B8" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="C8" t="s">
         <v>462</v>
       </c>
       <c r="D8" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E8" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F8" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="G8" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="H8" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="I8" t="s">
         <v>4</v>
@@ -21507,28 +21513,28 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="B9" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="C9" t="s">
         <v>462</v>
       </c>
       <c r="D9" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E9" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F9" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="G9" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="H9" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="I9" t="s">
         <v>4</v>
@@ -21542,28 +21548,28 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="B10" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="C10" t="s">
         <v>462</v>
       </c>
       <c r="D10" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E10" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F10" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="G10" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="H10" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="I10" t="s">
         <v>4</v>
@@ -21577,28 +21583,28 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="B11" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="C11" t="s">
         <v>462</v>
       </c>
       <c r="D11" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E11" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F11" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="G11" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="H11" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="I11" t="s">
         <v>4</v>
@@ -21612,28 +21618,28 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="B12" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="C12" t="s">
         <v>462</v>
       </c>
       <c r="D12" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E12" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F12" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="G12" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="H12" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="I12" t="s">
         <v>4</v>
@@ -21647,25 +21653,25 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="B13" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="C13" t="s">
         <v>462</v>
       </c>
       <c r="D13" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E13" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F13" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="G13" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="H13" t="s">
         <v>70</v>
@@ -21682,28 +21688,28 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="B14" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="C14" t="s">
         <v>462</v>
       </c>
       <c r="D14" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E14" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F14" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="G14" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="H14" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="I14" t="s">
         <v>4</v>
@@ -21717,28 +21723,28 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="B15" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="C15" t="s">
         <v>462</v>
       </c>
       <c r="D15" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E15" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F15" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="G15" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="H15" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="I15" t="s">
         <v>4</v>
@@ -21752,28 +21758,28 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="B16" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="C16" t="s">
         <v>462</v>
       </c>
       <c r="D16" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E16" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F16" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="G16" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="H16" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="I16" t="s">
         <v>4</v>
@@ -21787,28 +21793,28 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="B17" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="C17" t="s">
         <v>462</v>
       </c>
       <c r="D17" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E17" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F17" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="G17" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="H17" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="I17" t="s">
         <v>4</v>
@@ -21822,25 +21828,25 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="B18" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="C18" t="s">
         <v>462</v>
       </c>
       <c r="D18" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E18" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F18" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="G18" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="H18" t="s">
         <v>70</v>
@@ -21857,31 +21863,31 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="B19" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="C19" t="s">
         <v>462</v>
       </c>
       <c r="D19" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E19" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F19" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="G19" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="H19" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="I19" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="J19" t="s">
         <v>70</v>
@@ -21892,31 +21898,31 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="B20" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="C20" t="s">
         <v>462</v>
       </c>
       <c r="D20" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E20" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F20" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="G20" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="H20" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="I20" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="J20" t="s">
         <v>70</v>
@@ -21927,31 +21933,31 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="B21" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="C21" t="s">
         <v>462</v>
       </c>
       <c r="D21" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E21" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F21" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="G21" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="H21" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="I21" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="J21" t="s">
         <v>70</v>
@@ -21962,28 +21968,28 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="B22" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="C22" t="s">
         <v>462</v>
       </c>
       <c r="D22" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E22" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F22" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="G22" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="H22" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="I22" t="s">
         <v>4</v>
@@ -21997,28 +22003,28 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="B23" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="C23" t="s">
         <v>462</v>
       </c>
       <c r="D23" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E23" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F23" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="G23" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="H23" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="I23" t="s">
         <v>4</v>
@@ -22032,25 +22038,25 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="B24" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="C24" t="s">
         <v>462</v>
       </c>
       <c r="D24" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E24" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F24" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="G24" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="H24" t="s">
         <v>70</v>
@@ -22067,25 +22073,25 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="B25" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="C25" t="s">
         <v>462</v>
       </c>
       <c r="D25" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E25" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F25" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="G25" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="H25" t="s">
         <v>70</v>
@@ -22102,25 +22108,25 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="B26" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="C26" t="s">
         <v>462</v>
       </c>
       <c r="D26" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E26" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F26" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="G26" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="H26" t="s">
         <v>70</v>
@@ -22137,25 +22143,25 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="B27" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C27" t="s">
         <v>462</v>
       </c>
       <c r="D27" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E27" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F27" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="G27" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="H27" t="s">
         <v>70</v>
@@ -22172,25 +22178,25 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="B28" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="C28" t="s">
         <v>462</v>
       </c>
       <c r="D28" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E28" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F28" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="G28" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="H28" t="s">
         <v>70</v>
@@ -22207,28 +22213,28 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="B29" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="C29" t="s">
         <v>462</v>
       </c>
       <c r="D29" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E29" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F29" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="G29" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="H29" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="I29" t="s">
         <v>4</v>
@@ -22242,28 +22248,28 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C30" t="s">
+        <v>462</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E30" t="s">
+        <v>2149</v>
+      </c>
+      <c r="F30" t="s">
+        <v>2279</v>
+      </c>
+      <c r="G30" t="s">
+        <v>2280</v>
+      </c>
+      <c r="H30" t="s">
         <v>2276</v>
-      </c>
-      <c r="B30" t="s">
-        <v>2277</v>
-      </c>
-      <c r="C30" t="s">
-        <v>462</v>
-      </c>
-      <c r="D30" t="s">
-        <v>2147</v>
-      </c>
-      <c r="E30" t="s">
-        <v>2148</v>
-      </c>
-      <c r="F30" t="s">
-        <v>2278</v>
-      </c>
-      <c r="G30" t="s">
-        <v>2279</v>
-      </c>
-      <c r="H30" t="s">
-        <v>2275</v>
       </c>
       <c r="I30" t="s">
         <v>4</v>
@@ -22277,28 +22283,28 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="B31" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="C31" t="s">
         <v>462</v>
       </c>
       <c r="D31" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E31" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F31" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="G31" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="H31" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="I31" t="s">
         <v>4</v>
@@ -22312,28 +22318,28 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="B32" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="C32" t="s">
         <v>462</v>
       </c>
       <c r="D32" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E32" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F32" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="G32" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="H32" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="I32" t="s">
         <v>4</v>
@@ -22347,28 +22353,28 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="B33" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="C33" t="s">
         <v>462</v>
       </c>
       <c r="D33" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E33" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F33" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="G33" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="H33" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="I33" t="s">
         <v>4</v>
@@ -22382,28 +22388,28 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="B34" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="C34" t="s">
         <v>462</v>
       </c>
       <c r="D34" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E34" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F34" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="G34" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="H34" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="I34" t="s">
         <v>4</v>
@@ -22417,28 +22423,28 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="B35" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="C35" t="s">
         <v>462</v>
       </c>
       <c r="D35" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E35" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F35" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="G35" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="H35" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="I35" t="s">
         <v>4</v>
@@ -22452,28 +22458,28 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2305</v>
+      </c>
+      <c r="C36" t="s">
+        <v>462</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E36" t="s">
+        <v>2149</v>
+      </c>
+      <c r="F36" t="s">
+        <v>2306</v>
+      </c>
+      <c r="G36" t="s">
+        <v>2307</v>
+      </c>
+      <c r="H36" t="s">
         <v>2303</v>
-      </c>
-      <c r="B36" t="s">
-        <v>2304</v>
-      </c>
-      <c r="C36" t="s">
-        <v>462</v>
-      </c>
-      <c r="D36" t="s">
-        <v>2147</v>
-      </c>
-      <c r="E36" t="s">
-        <v>2148</v>
-      </c>
-      <c r="F36" t="s">
-        <v>2305</v>
-      </c>
-      <c r="G36" t="s">
-        <v>2306</v>
-      </c>
-      <c r="H36" t="s">
-        <v>2302</v>
       </c>
       <c r="I36" t="s">
         <v>4</v>
@@ -22487,28 +22493,28 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="B37" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="C37" t="s">
         <v>462</v>
       </c>
       <c r="D37" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E37" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F37" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="G37" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="H37" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="I37" t="s">
         <v>4</v>
@@ -22522,28 +22528,28 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="B38" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="C38" t="s">
         <v>462</v>
       </c>
       <c r="D38" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E38" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F38" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="G38" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="H38" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="I38" t="s">
         <v>4</v>
@@ -22557,28 +22563,28 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="B39" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="C39" t="s">
         <v>462</v>
       </c>
       <c r="D39" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E39" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F39" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="G39" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="H39" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="I39" t="s">
         <v>4</v>
@@ -22592,28 +22598,28 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="B40" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="C40" t="s">
         <v>462</v>
       </c>
       <c r="D40" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E40" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F40" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G40" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="H40" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I40" t="s">
         <v>4</v>
@@ -22627,28 +22633,28 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>2327</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2328</v>
+      </c>
+      <c r="C41" t="s">
+        <v>462</v>
+      </c>
+      <c r="D41" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E41" t="s">
+        <v>2149</v>
+      </c>
+      <c r="F41" t="s">
+        <v>2329</v>
+      </c>
+      <c r="G41" t="s">
+        <v>2330</v>
+      </c>
+      <c r="H41" t="s">
         <v>2326</v>
-      </c>
-      <c r="B41" t="s">
-        <v>2327</v>
-      </c>
-      <c r="C41" t="s">
-        <v>462</v>
-      </c>
-      <c r="D41" t="s">
-        <v>2147</v>
-      </c>
-      <c r="E41" t="s">
-        <v>2148</v>
-      </c>
-      <c r="F41" t="s">
-        <v>2328</v>
-      </c>
-      <c r="G41" t="s">
-        <v>2329</v>
-      </c>
-      <c r="H41" t="s">
-        <v>2325</v>
       </c>
       <c r="I41" t="s">
         <v>4</v>
@@ -22662,28 +22668,28 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="B42" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="C42" t="s">
         <v>462</v>
       </c>
       <c r="D42" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E42" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F42" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="G42" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="H42" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I42" t="s">
         <v>4</v>
@@ -22697,28 +22703,28 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="B43" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="C43" t="s">
         <v>462</v>
       </c>
       <c r="D43" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E43" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F43" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="G43" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="H43" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I43" t="s">
         <v>4</v>
@@ -22732,28 +22738,28 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="B44" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="C44" t="s">
         <v>462</v>
       </c>
       <c r="D44" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E44" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F44" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="G44" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="H44" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I44" t="s">
         <v>4</v>
@@ -22767,28 +22773,28 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="B45" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="C45" t="s">
         <v>462</v>
       </c>
       <c r="D45" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E45" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F45" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="G45" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="H45" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I45" t="s">
         <v>4</v>
@@ -22802,28 +22808,28 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="B46" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="C46" t="s">
         <v>462</v>
       </c>
       <c r="D46" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E46" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F46" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="G46" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="H46" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I46" t="s">
         <v>4</v>
@@ -22837,28 +22843,28 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="B47" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="C47" t="s">
         <v>462</v>
       </c>
       <c r="D47" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E47" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F47" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="G47" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="H47" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I47" t="s">
         <v>4</v>
@@ -22872,28 +22878,28 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="B48" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="C48" t="s">
         <v>462</v>
       </c>
       <c r="D48" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E48" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F48" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="G48" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="H48" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I48" t="s">
         <v>4</v>
@@ -22907,28 +22913,28 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="B49" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="C49" t="s">
         <v>462</v>
       </c>
       <c r="D49" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E49" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F49" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="G49" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="H49" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I49" t="s">
         <v>4</v>
@@ -22942,28 +22948,28 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="B50" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="C50" t="s">
         <v>462</v>
       </c>
       <c r="D50" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E50" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F50" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="G50" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="H50" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I50" t="s">
         <v>4</v>
@@ -22977,28 +22983,28 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="B51" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="C51" t="s">
         <v>462</v>
       </c>
       <c r="D51" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E51" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F51" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="G51" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="H51" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I51" t="s">
         <v>4</v>
@@ -23012,28 +23018,28 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="B52" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="C52" t="s">
         <v>462</v>
       </c>
       <c r="D52" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E52" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F52" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="G52" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="H52" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I52" t="s">
         <v>4</v>
@@ -23047,28 +23053,28 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="B53" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="C53" t="s">
         <v>462</v>
       </c>
       <c r="D53" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E53" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F53" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="G53" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="H53" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I53" t="s">
         <v>4</v>
@@ -23082,28 +23088,28 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="B54" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="C54" t="s">
         <v>462</v>
       </c>
       <c r="D54" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E54" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F54" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="G54" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="H54" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I54" t="s">
         <v>4</v>
@@ -23117,28 +23123,28 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="B55" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="C55" t="s">
         <v>462</v>
       </c>
       <c r="D55" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E55" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F55" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="G55" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="H55" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I55" t="s">
         <v>4</v>
@@ -23152,28 +23158,28 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="B56" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="C56" t="s">
         <v>462</v>
       </c>
       <c r="D56" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E56" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F56" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="G56" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="H56" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I56" t="s">
         <v>4</v>
@@ -23187,28 +23193,28 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="B57" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="C57" t="s">
         <v>462</v>
       </c>
       <c r="D57" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E57" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F57" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="G57" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="H57" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I57" t="s">
         <v>4</v>
@@ -23217,33 +23223,33 @@
         <v>9</v>
       </c>
       <c r="K57" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="B58" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="C58" t="s">
         <v>462</v>
       </c>
       <c r="D58" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E58" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F58" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="G58" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="H58" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I58" t="s">
         <v>4</v>
@@ -23257,28 +23263,28 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="B59" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="C59" t="s">
         <v>462</v>
       </c>
       <c r="D59" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E59" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F59" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="G59" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="H59" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I59" t="s">
         <v>4</v>
@@ -23292,28 +23298,28 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="B60" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="C60" t="s">
         <v>462</v>
       </c>
       <c r="D60" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E60" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F60" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="G60" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="H60" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I60" t="s">
         <v>5</v>
@@ -23327,28 +23333,28 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="B61" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="C61" t="s">
         <v>462</v>
       </c>
       <c r="D61" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E61" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F61" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="G61" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="H61" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I61" t="s">
         <v>5</v>
@@ -23362,28 +23368,28 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="B62" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="C62" t="s">
         <v>462</v>
       </c>
       <c r="D62" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E62" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F62" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="G62" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="H62" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I62" t="s">
         <v>5</v>
@@ -23397,28 +23403,28 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="B63" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="C63" t="s">
         <v>462</v>
       </c>
       <c r="D63" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E63" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F63" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="G63" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="H63" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I63" t="s">
         <v>5</v>
@@ -23432,28 +23438,28 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="B64" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="C64" t="s">
         <v>462</v>
       </c>
       <c r="D64" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E64" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F64" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="G64" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="H64" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I64" t="s">
         <v>5</v>
@@ -23467,28 +23473,28 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="B65" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="C65" t="s">
         <v>462</v>
       </c>
       <c r="D65" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="E65" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="F65" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="G65" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="H65" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="I65" t="s">
         <v>5</v>
@@ -23505,7 +23511,7 @@
         <v>144</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>70</v>
@@ -23526,10 +23532,10 @@
         <v>70</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>148</v>
@@ -23593,25 +23599,25 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="B2" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="C2" t="s">
         <v>462</v>
       </c>
       <c r="D2" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E2" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F2" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="G2" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="H2" t="s">
         <v>70</v>
@@ -23628,28 +23634,28 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="B3" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="C3" t="s">
         <v>462</v>
       </c>
       <c r="D3" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E3" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F3" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="G3" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="H3" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="I3" t="s">
         <v>4</v>
@@ -23663,25 +23669,25 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="B4" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="C4" t="s">
         <v>462</v>
       </c>
       <c r="D4" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E4" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F4" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="G4" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="H4" t="s">
         <v>70</v>
@@ -23698,25 +23704,25 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="B5" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="C5" t="s">
         <v>462</v>
       </c>
       <c r="D5" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E5" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F5" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="G5" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="H5" t="s">
         <v>70</v>
@@ -23733,25 +23739,25 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="B6" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="C6" t="s">
         <v>462</v>
       </c>
       <c r="D6" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E6" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F6" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="G6" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="H6" t="s">
         <v>70</v>
@@ -23768,28 +23774,28 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="B7" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="C7" t="s">
         <v>462</v>
       </c>
       <c r="D7" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E7" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F7" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="G7" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="H7" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="I7" t="s">
         <v>4</v>
@@ -23803,25 +23809,25 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="B8" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="C8" t="s">
         <v>462</v>
       </c>
       <c r="D8" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E8" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F8" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="G8" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="H8" t="s">
         <v>70</v>
@@ -23838,25 +23844,25 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="B9" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="C9" t="s">
         <v>462</v>
       </c>
       <c r="D9" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E9" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F9" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="G9" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="H9" t="s">
         <v>70</v>
@@ -23873,28 +23879,28 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="B10" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="C10" t="s">
         <v>462</v>
       </c>
       <c r="D10" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E10" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F10" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="G10" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="H10" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="I10" t="s">
         <v>4</v>
@@ -23908,28 +23914,28 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="B11" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="C11" t="s">
         <v>462</v>
       </c>
       <c r="D11" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E11" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F11" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="G11" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="H11" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="I11" t="s">
         <v>4</v>
@@ -23943,25 +23949,25 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="B12" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="C12" t="s">
         <v>462</v>
       </c>
       <c r="D12" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E12" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F12" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="G12" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="H12" t="s">
         <v>70</v>
@@ -23978,28 +23984,28 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="B13" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="C13" t="s">
         <v>462</v>
       </c>
       <c r="D13" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E13" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F13" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="G13" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="H13" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="I13" t="s">
         <v>4</v>
@@ -24013,25 +24019,25 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="B14" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="C14" t="s">
         <v>462</v>
       </c>
       <c r="D14" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E14" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F14" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="G14" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="H14" t="s">
         <v>70</v>
@@ -24048,25 +24054,25 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="B15" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="C15" t="s">
         <v>462</v>
       </c>
       <c r="D15" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E15" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F15" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="G15" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="H15" t="s">
         <v>70</v>
@@ -24083,28 +24089,28 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="B16" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="C16" t="s">
         <v>462</v>
       </c>
       <c r="D16" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E16" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F16" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="G16" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="H16" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="I16" t="s">
         <v>4</v>
@@ -24118,25 +24124,25 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="B17" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="C17" t="s">
         <v>462</v>
       </c>
       <c r="D17" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E17" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F17" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="G17" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="H17" t="s">
         <v>70</v>
@@ -24153,28 +24159,28 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="B18" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="C18" t="s">
         <v>462</v>
       </c>
       <c r="D18" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E18" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F18" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="G18" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="H18" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="I18" t="s">
         <v>4</v>
@@ -24188,28 +24194,28 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="B19" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="C19" t="s">
         <v>462</v>
       </c>
       <c r="D19" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E19" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F19" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="G19" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="H19" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="I19" t="s">
         <v>4</v>
@@ -24223,25 +24229,25 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="B20" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="C20" t="s">
         <v>462</v>
       </c>
       <c r="D20" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E20" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F20" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="G20" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="H20" t="s">
         <v>70</v>
@@ -24258,25 +24264,25 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="B21" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="C21" t="s">
         <v>462</v>
       </c>
       <c r="D21" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E21" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F21" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="G21" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="H21" t="s">
         <v>70</v>
@@ -24288,30 +24294,30 @@
         <v>8</v>
       </c>
       <c r="K21" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="B22" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="C22" t="s">
         <v>462</v>
       </c>
       <c r="D22" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E22" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F22" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="G22" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="H22" t="s">
         <v>70</v>
@@ -24328,28 +24334,28 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="B23" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="C23" t="s">
         <v>462</v>
       </c>
       <c r="D23" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E23" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F23" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="G23" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="H23" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="I23" t="s">
         <v>4</v>
@@ -24363,28 +24369,28 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="B24" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="C24" t="s">
         <v>462</v>
       </c>
       <c r="D24" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E24" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F24" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="G24" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="H24" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="I24" t="s">
         <v>4</v>
@@ -24398,28 +24404,28 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="B25" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="C25" t="s">
         <v>462</v>
       </c>
       <c r="D25" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E25" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F25" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="G25" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="H25" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="I25" t="s">
         <v>4</v>
@@ -24433,28 +24439,28 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="B26" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="C26" t="s">
         <v>462</v>
       </c>
       <c r="D26" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E26" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F26" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="G26" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="H26" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="I26" t="s">
         <v>4</v>
@@ -24463,33 +24469,33 @@
         <v>8</v>
       </c>
       <c r="K26" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="B27" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="C27" t="s">
         <v>462</v>
       </c>
       <c r="D27" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E27" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F27" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="G27" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="H27" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="I27" t="s">
         <v>4</v>
@@ -24498,33 +24504,33 @@
         <v>8</v>
       </c>
       <c r="K27" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="B28" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="C28" t="s">
         <v>462</v>
       </c>
       <c r="D28" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E28" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F28" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="G28" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="H28" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="I28" t="s">
         <v>4</v>
@@ -24533,33 +24539,33 @@
         <v>8</v>
       </c>
       <c r="K28" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="B29" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="C29" t="s">
         <v>462</v>
       </c>
       <c r="D29" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E29" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F29" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="G29" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="H29" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="I29" t="s">
         <v>4</v>
@@ -24568,33 +24574,33 @@
         <v>8</v>
       </c>
       <c r="K29" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="B30" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="C30" t="s">
         <v>462</v>
       </c>
       <c r="D30" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E30" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F30" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="G30" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="H30" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="I30" t="s">
         <v>4</v>
@@ -24603,33 +24609,33 @@
         <v>8</v>
       </c>
       <c r="K30" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="B31" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="C31" t="s">
         <v>462</v>
       </c>
       <c r="D31" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E31" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F31" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="G31" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="H31" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="I31" t="s">
         <v>4</v>
@@ -24638,30 +24644,30 @@
         <v>8</v>
       </c>
       <c r="K31" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
       <c r="B32" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="C32" t="s">
         <v>462</v>
       </c>
       <c r="D32" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E32" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F32" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="G32" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="H32" t="s">
         <v>70</v>
@@ -24678,28 +24684,28 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="B33" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="C33" t="s">
         <v>462</v>
       </c>
       <c r="D33" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E33" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F33" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="G33" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="H33" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="I33" t="s">
         <v>4</v>
@@ -24713,28 +24719,28 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="B34" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="C34" t="s">
         <v>462</v>
       </c>
       <c r="D34" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E34" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F34" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="G34" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="H34" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="I34" t="s">
         <v>4</v>
@@ -24748,28 +24754,28 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="B35" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
       <c r="C35" t="s">
         <v>462</v>
       </c>
       <c r="D35" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="E35" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="F35" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="G35" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
       <c r="H35" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
       <c r="I35" t="s">
         <v>4</v>
@@ -24786,7 +24792,7 @@
         <v>144</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>2591</v>
+        <v>2592</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>70</v>
@@ -24807,10 +24813,10 @@
         <v>70</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>148</v>
@@ -24875,25 +24881,25 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2594</v>
+        <v>2595</v>
       </c>
       <c r="B2" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
       <c r="C2" t="s">
         <v>462</v>
       </c>
       <c r="D2" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E2" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F2" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="G2" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
       <c r="H2" t="s">
         <v>70</v>
@@ -24910,25 +24916,25 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2600</v>
+        <v>2601</v>
       </c>
       <c r="B3" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="C3" t="s">
         <v>462</v>
       </c>
       <c r="D3" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E3" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F3" t="s">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="G3" t="s">
-        <v>2603</v>
+        <v>2604</v>
       </c>
       <c r="H3" t="s">
         <v>70</v>
@@ -24945,25 +24951,25 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2604</v>
+        <v>2605</v>
       </c>
       <c r="B4" t="s">
-        <v>2605</v>
+        <v>2606</v>
       </c>
       <c r="C4" t="s">
         <v>462</v>
       </c>
       <c r="D4" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E4" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F4" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="G4" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
       <c r="H4" t="s">
         <v>70</v>
@@ -24980,25 +24986,25 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2608</v>
+        <v>2609</v>
       </c>
       <c r="B5" t="s">
-        <v>2609</v>
+        <v>2610</v>
       </c>
       <c r="C5" t="s">
         <v>462</v>
       </c>
       <c r="D5" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E5" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F5" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="G5" t="s">
-        <v>2611</v>
+        <v>2612</v>
       </c>
       <c r="H5" t="s">
         <v>70</v>
@@ -25015,25 +25021,25 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="B6" t="s">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="C6" t="s">
         <v>462</v>
       </c>
       <c r="D6" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E6" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F6" t="s">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="G6" t="s">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="H6" t="s">
         <v>70</v>
@@ -25050,28 +25056,28 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2616</v>
+        <v>2617</v>
       </c>
       <c r="B7" t="s">
-        <v>2617</v>
+        <v>2618</v>
       </c>
       <c r="C7" t="s">
         <v>462</v>
       </c>
       <c r="D7" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E7" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="F7" t="s">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="G7" t="s">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="H7" t="s">
-        <v>2621</v>
+        <v>2622</v>
       </c>
       <c r="I7" t="s">
         <v>4</v>
@@ -25085,25 +25091,25 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2622</v>
+        <v>2623</v>
       </c>
       <c r="B8" t="s">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="C8" t="s">
         <v>462</v>
       </c>
       <c r="D8" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E8" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="F8" t="s">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="G8" t="s">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="H8" t="s">
         <v>70</v>
@@ -25112,36 +25118,36 @@
         <v>4</v>
       </c>
       <c r="J8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K8" t="s">
-        <v>70</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2626</v>
+        <v>2628</v>
       </c>
       <c r="B9" t="s">
-        <v>2627</v>
+        <v>2629</v>
       </c>
       <c r="C9" t="s">
         <v>462</v>
       </c>
       <c r="D9" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E9" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="F9" t="s">
-        <v>2628</v>
+        <v>2630</v>
       </c>
       <c r="G9" t="s">
-        <v>2629</v>
+        <v>2631</v>
       </c>
       <c r="H9" t="s">
-        <v>2630</v>
+        <v>2632</v>
       </c>
       <c r="I9" t="s">
         <v>4</v>
@@ -25155,25 +25161,25 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2631</v>
+        <v>2633</v>
       </c>
       <c r="B10" t="s">
-        <v>2632</v>
+        <v>2634</v>
       </c>
       <c r="C10" t="s">
         <v>462</v>
       </c>
       <c r="D10" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E10" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F10" t="s">
-        <v>2633</v>
+        <v>2635</v>
       </c>
       <c r="G10" t="s">
-        <v>2634</v>
+        <v>2636</v>
       </c>
       <c r="H10" t="s">
         <v>70</v>
@@ -25190,25 +25196,25 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2635</v>
+        <v>2637</v>
       </c>
       <c r="B11" t="s">
-        <v>2636</v>
+        <v>2638</v>
       </c>
       <c r="C11" t="s">
         <v>462</v>
       </c>
       <c r="D11" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E11" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F11" t="s">
-        <v>2637</v>
+        <v>2639</v>
       </c>
       <c r="G11" t="s">
-        <v>2638</v>
+        <v>2640</v>
       </c>
       <c r="H11" t="s">
         <v>70</v>
@@ -25225,25 +25231,25 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2639</v>
+        <v>2641</v>
       </c>
       <c r="B12" t="s">
-        <v>2640</v>
+        <v>2642</v>
       </c>
       <c r="C12" t="s">
         <v>462</v>
       </c>
       <c r="D12" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E12" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F12" t="s">
-        <v>2641</v>
+        <v>2643</v>
       </c>
       <c r="G12" t="s">
-        <v>2642</v>
+        <v>2644</v>
       </c>
       <c r="H12" t="s">
         <v>70</v>
@@ -25260,28 +25266,28 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2643</v>
+        <v>2645</v>
       </c>
       <c r="B13" t="s">
-        <v>2644</v>
+        <v>2646</v>
       </c>
       <c r="C13" t="s">
         <v>462</v>
       </c>
       <c r="D13" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E13" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F13" t="s">
-        <v>2645</v>
+        <v>2647</v>
       </c>
       <c r="G13" t="s">
-        <v>2646</v>
+        <v>2648</v>
       </c>
       <c r="H13" t="s">
-        <v>2647</v>
+        <v>2649</v>
       </c>
       <c r="I13" t="s">
         <v>4</v>
@@ -25295,28 +25301,28 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2648</v>
+        <v>2650</v>
       </c>
       <c r="B14" t="s">
-        <v>2649</v>
+        <v>2651</v>
       </c>
       <c r="C14" t="s">
         <v>462</v>
       </c>
       <c r="D14" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E14" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F14" t="s">
-        <v>2650</v>
+        <v>2652</v>
       </c>
       <c r="G14" t="s">
-        <v>2651</v>
+        <v>2653</v>
       </c>
       <c r="H14" t="s">
-        <v>2652</v>
+        <v>2654</v>
       </c>
       <c r="I14" t="s">
         <v>4</v>
@@ -25330,28 +25336,28 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>2653</v>
+        <v>2655</v>
       </c>
       <c r="B15" t="s">
-        <v>2654</v>
+        <v>2656</v>
       </c>
       <c r="C15" t="s">
         <v>462</v>
       </c>
       <c r="D15" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E15" t="s">
-        <v>2655</v>
+        <v>2657</v>
       </c>
       <c r="F15" t="s">
-        <v>2656</v>
+        <v>2658</v>
       </c>
       <c r="G15" t="s">
-        <v>2657</v>
+        <v>2659</v>
       </c>
       <c r="H15" t="s">
-        <v>2658</v>
+        <v>2660</v>
       </c>
       <c r="I15" t="s">
         <v>4</v>
@@ -25365,28 +25371,28 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2659</v>
+        <v>2661</v>
       </c>
       <c r="B16" t="s">
-        <v>2660</v>
+        <v>2662</v>
       </c>
       <c r="C16" t="s">
         <v>462</v>
       </c>
       <c r="D16" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E16" t="s">
-        <v>2661</v>
+        <v>2663</v>
       </c>
       <c r="F16" t="s">
-        <v>2662</v>
+        <v>2664</v>
       </c>
       <c r="G16" t="s">
-        <v>2663</v>
+        <v>2665</v>
       </c>
       <c r="H16" t="s">
-        <v>2664</v>
+        <v>2666</v>
       </c>
       <c r="I16" t="s">
         <v>4</v>
@@ -25400,25 +25406,25 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2665</v>
+        <v>2667</v>
       </c>
       <c r="B17" t="s">
-        <v>2666</v>
+        <v>2668</v>
       </c>
       <c r="C17" t="s">
         <v>462</v>
       </c>
       <c r="D17" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E17" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F17" t="s">
-        <v>2667</v>
+        <v>2669</v>
       </c>
       <c r="G17" t="s">
-        <v>2668</v>
+        <v>2670</v>
       </c>
       <c r="H17" t="s">
         <v>70</v>
@@ -25435,28 +25441,28 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2669</v>
+        <v>2671</v>
       </c>
       <c r="B18" t="s">
-        <v>2670</v>
+        <v>2672</v>
       </c>
       <c r="C18" t="s">
         <v>462</v>
       </c>
       <c r="D18" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E18" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F18" t="s">
-        <v>2671</v>
+        <v>2673</v>
       </c>
       <c r="G18" t="s">
-        <v>2672</v>
+        <v>2674</v>
       </c>
       <c r="H18" t="s">
-        <v>2673</v>
+        <v>2675</v>
       </c>
       <c r="I18" t="s">
         <v>4</v>
@@ -25470,28 +25476,28 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2674</v>
+        <v>2676</v>
       </c>
       <c r="B19" t="s">
-        <v>2675</v>
+        <v>2677</v>
       </c>
       <c r="C19" t="s">
         <v>462</v>
       </c>
       <c r="D19" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E19" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F19" t="s">
-        <v>2676</v>
+        <v>2678</v>
       </c>
       <c r="G19" t="s">
-        <v>2677</v>
+        <v>2679</v>
       </c>
       <c r="H19" t="s">
-        <v>2678</v>
+        <v>2680</v>
       </c>
       <c r="I19" t="s">
         <v>4</v>
@@ -25505,28 +25511,28 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2679</v>
+        <v>2681</v>
       </c>
       <c r="B20" t="s">
+        <v>2682</v>
+      </c>
+      <c r="C20" t="s">
+        <v>462</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2598</v>
+      </c>
+      <c r="F20" t="s">
+        <v>2683</v>
+      </c>
+      <c r="G20" t="s">
+        <v>2684</v>
+      </c>
+      <c r="H20" t="s">
         <v>2680</v>
-      </c>
-      <c r="C20" t="s">
-        <v>462</v>
-      </c>
-      <c r="D20" t="s">
-        <v>2596</v>
-      </c>
-      <c r="E20" t="s">
-        <v>2597</v>
-      </c>
-      <c r="F20" t="s">
-        <v>2681</v>
-      </c>
-      <c r="G20" t="s">
-        <v>2682</v>
-      </c>
-      <c r="H20" t="s">
-        <v>2678</v>
       </c>
       <c r="I20" t="s">
         <v>4</v>
@@ -25540,25 +25546,25 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2683</v>
+        <v>2685</v>
       </c>
       <c r="B21" t="s">
-        <v>2684</v>
+        <v>2686</v>
       </c>
       <c r="C21" t="s">
         <v>462</v>
       </c>
       <c r="D21" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E21" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F21" t="s">
-        <v>2685</v>
+        <v>2687</v>
       </c>
       <c r="G21" t="s">
-        <v>2686</v>
+        <v>2688</v>
       </c>
       <c r="H21" t="s">
         <v>70</v>
@@ -25575,28 +25581,28 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2687</v>
+        <v>2689</v>
       </c>
       <c r="B22" t="s">
-        <v>2688</v>
+        <v>2690</v>
       </c>
       <c r="C22" t="s">
         <v>462</v>
       </c>
       <c r="D22" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E22" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F22" t="s">
-        <v>2689</v>
+        <v>2691</v>
       </c>
       <c r="G22" t="s">
-        <v>2690</v>
+        <v>2692</v>
       </c>
       <c r="H22" t="s">
-        <v>2691</v>
+        <v>2693</v>
       </c>
       <c r="I22" t="s">
         <v>4</v>
@@ -25610,25 +25616,25 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2692</v>
+        <v>2694</v>
       </c>
       <c r="B23" t="s">
-        <v>2693</v>
+        <v>2695</v>
       </c>
       <c r="C23" t="s">
         <v>462</v>
       </c>
       <c r="D23" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E23" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F23" t="s">
-        <v>2694</v>
+        <v>2696</v>
       </c>
       <c r="G23" t="s">
-        <v>2695</v>
+        <v>2697</v>
       </c>
       <c r="H23" t="s">
         <v>70</v>
@@ -25645,28 +25651,28 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2696</v>
+        <v>2698</v>
       </c>
       <c r="B24" t="s">
-        <v>2697</v>
+        <v>2699</v>
       </c>
       <c r="C24" t="s">
         <v>462</v>
       </c>
       <c r="D24" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E24" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F24" t="s">
-        <v>2698</v>
+        <v>2700</v>
       </c>
       <c r="G24" t="s">
-        <v>2699</v>
+        <v>2701</v>
       </c>
       <c r="H24" t="s">
-        <v>2700</v>
+        <v>2702</v>
       </c>
       <c r="I24" t="s">
         <v>4</v>
@@ -25680,28 +25686,28 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2701</v>
+        <v>2703</v>
       </c>
       <c r="B25" t="s">
-        <v>2702</v>
+        <v>2704</v>
       </c>
       <c r="C25" t="s">
         <v>462</v>
       </c>
       <c r="D25" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E25" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F25" t="s">
-        <v>2703</v>
+        <v>2705</v>
       </c>
       <c r="G25" t="s">
-        <v>2704</v>
+        <v>2706</v>
       </c>
       <c r="H25" t="s">
-        <v>2678</v>
+        <v>2680</v>
       </c>
       <c r="I25" t="s">
         <v>4</v>
@@ -25710,30 +25716,30 @@
         <v>9</v>
       </c>
       <c r="K25" t="s">
-        <v>2705</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2706</v>
+        <v>2708</v>
       </c>
       <c r="B26" t="s">
-        <v>2707</v>
+        <v>2709</v>
       </c>
       <c r="C26" t="s">
         <v>462</v>
       </c>
       <c r="D26" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E26" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F26" t="s">
-        <v>2708</v>
+        <v>2710</v>
       </c>
       <c r="G26" t="s">
-        <v>2709</v>
+        <v>2711</v>
       </c>
       <c r="H26" t="s">
         <v>70</v>
@@ -25750,25 +25756,25 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2710</v>
+        <v>2712</v>
       </c>
       <c r="B27" t="s">
-        <v>2711</v>
+        <v>2713</v>
       </c>
       <c r="C27" t="s">
         <v>462</v>
       </c>
       <c r="D27" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E27" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F27" t="s">
-        <v>2712</v>
+        <v>2714</v>
       </c>
       <c r="G27" t="s">
-        <v>2713</v>
+        <v>2715</v>
       </c>
       <c r="H27" t="s">
         <v>70</v>
@@ -25785,28 +25791,28 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="B28" t="s">
-        <v>2715</v>
+        <v>2717</v>
       </c>
       <c r="C28" t="s">
         <v>462</v>
       </c>
       <c r="D28" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E28" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F28" t="s">
-        <v>2716</v>
+        <v>2718</v>
       </c>
       <c r="G28" t="s">
-        <v>2717</v>
+        <v>2719</v>
       </c>
       <c r="H28" t="s">
-        <v>2718</v>
+        <v>2720</v>
       </c>
       <c r="I28" t="s">
         <v>4</v>
@@ -25820,28 +25826,28 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>2719</v>
+        <v>2721</v>
       </c>
       <c r="B29" t="s">
-        <v>2720</v>
+        <v>2722</v>
       </c>
       <c r="C29" t="s">
         <v>462</v>
       </c>
       <c r="D29" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E29" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F29" t="s">
-        <v>2721</v>
+        <v>2723</v>
       </c>
       <c r="G29" t="s">
-        <v>2722</v>
+        <v>2724</v>
       </c>
       <c r="H29" t="s">
-        <v>2723</v>
+        <v>2725</v>
       </c>
       <c r="I29" t="s">
         <v>4</v>
@@ -25855,28 +25861,28 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>2724</v>
+        <v>2726</v>
       </c>
       <c r="B30" t="s">
-        <v>2725</v>
+        <v>2727</v>
       </c>
       <c r="C30" t="s">
         <v>462</v>
       </c>
       <c r="D30" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E30" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F30" t="s">
-        <v>2726</v>
+        <v>2728</v>
       </c>
       <c r="G30" t="s">
-        <v>2727</v>
+        <v>2729</v>
       </c>
       <c r="H30" t="s">
-        <v>2728</v>
+        <v>2730</v>
       </c>
       <c r="I30" t="s">
         <v>4</v>
@@ -25890,63 +25896,63 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>2729</v>
+        <v>2731</v>
       </c>
       <c r="B31" t="s">
-        <v>2730</v>
+        <v>2732</v>
       </c>
       <c r="C31" t="s">
         <v>462</v>
       </c>
       <c r="D31" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E31" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F31" t="s">
-        <v>2731</v>
+        <v>2733</v>
       </c>
       <c r="G31" t="s">
-        <v>2732</v>
+        <v>2734</v>
       </c>
       <c r="H31" t="s">
-        <v>2733</v>
+        <v>2735</v>
       </c>
       <c r="I31" t="s">
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K31" t="s">
-        <v>70</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>2734</v>
+        <v>2737</v>
       </c>
       <c r="B32" t="s">
-        <v>2735</v>
+        <v>2738</v>
       </c>
       <c r="C32" t="s">
         <v>462</v>
       </c>
       <c r="D32" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E32" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F32" t="s">
-        <v>2736</v>
+        <v>2739</v>
       </c>
       <c r="G32" t="s">
-        <v>2737</v>
+        <v>2740</v>
       </c>
       <c r="H32" t="s">
-        <v>2738</v>
+        <v>2741</v>
       </c>
       <c r="I32" t="s">
         <v>4</v>
@@ -25955,33 +25961,33 @@
         <v>9</v>
       </c>
       <c r="K32" t="s">
-        <v>2739</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>2740</v>
+        <v>2742</v>
       </c>
       <c r="B33" t="s">
+        <v>2743</v>
+      </c>
+      <c r="C33" t="s">
+        <v>462</v>
+      </c>
+      <c r="D33" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E33" t="s">
+        <v>2598</v>
+      </c>
+      <c r="F33" t="s">
+        <v>2744</v>
+      </c>
+      <c r="G33" t="s">
+        <v>2745</v>
+      </c>
+      <c r="H33" t="s">
         <v>2741</v>
-      </c>
-      <c r="C33" t="s">
-        <v>462</v>
-      </c>
-      <c r="D33" t="s">
-        <v>2596</v>
-      </c>
-      <c r="E33" t="s">
-        <v>2597</v>
-      </c>
-      <c r="F33" t="s">
-        <v>2742</v>
-      </c>
-      <c r="G33" t="s">
-        <v>2743</v>
-      </c>
-      <c r="H33" t="s">
-        <v>2738</v>
       </c>
       <c r="I33" t="s">
         <v>4</v>
@@ -25990,33 +25996,33 @@
         <v>9</v>
       </c>
       <c r="K33" t="s">
-        <v>2739</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>2746</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2747</v>
+      </c>
+      <c r="C34" t="s">
+        <v>462</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2597</v>
+      </c>
+      <c r="E34" t="s">
+        <v>2598</v>
+      </c>
+      <c r="F34" t="s">
         <v>2744</v>
       </c>
-      <c r="B34" t="s">
-        <v>2745</v>
-      </c>
-      <c r="C34" t="s">
-        <v>462</v>
-      </c>
-      <c r="D34" t="s">
-        <v>2596</v>
-      </c>
-      <c r="E34" t="s">
-        <v>2597</v>
-      </c>
-      <c r="F34" t="s">
-        <v>2742</v>
-      </c>
       <c r="G34" t="s">
-        <v>2746</v>
+        <v>2748</v>
       </c>
       <c r="H34" t="s">
-        <v>2738</v>
+        <v>2741</v>
       </c>
       <c r="I34" t="s">
         <v>4</v>
@@ -26030,28 +26036,28 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2747</v>
+        <v>2749</v>
       </c>
       <c r="B35" t="s">
-        <v>2748</v>
+        <v>2750</v>
       </c>
       <c r="C35" t="s">
         <v>462</v>
       </c>
       <c r="D35" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E35" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F35" t="s">
-        <v>2742</v>
+        <v>2744</v>
       </c>
       <c r="G35" t="s">
-        <v>2749</v>
+        <v>2751</v>
       </c>
       <c r="H35" t="s">
-        <v>2738</v>
+        <v>2741</v>
       </c>
       <c r="I35" t="s">
         <v>4</v>
@@ -26065,28 +26071,28 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>2750</v>
+        <v>2752</v>
       </c>
       <c r="B36" t="s">
-        <v>2751</v>
+        <v>2753</v>
       </c>
       <c r="C36" t="s">
         <v>462</v>
       </c>
       <c r="D36" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E36" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F36" t="s">
-        <v>2742</v>
+        <v>2744</v>
       </c>
       <c r="G36" t="s">
-        <v>2752</v>
+        <v>2754</v>
       </c>
       <c r="H36" t="s">
-        <v>2738</v>
+        <v>2741</v>
       </c>
       <c r="I36" t="s">
         <v>4</v>
@@ -26100,28 +26106,28 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>2753</v>
+        <v>2755</v>
       </c>
       <c r="B37" t="s">
-        <v>2754</v>
+        <v>2756</v>
       </c>
       <c r="C37" t="s">
         <v>462</v>
       </c>
       <c r="D37" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E37" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F37" t="s">
-        <v>2742</v>
+        <v>2744</v>
       </c>
       <c r="G37" t="s">
-        <v>2755</v>
+        <v>2757</v>
       </c>
       <c r="H37" t="s">
-        <v>2738</v>
+        <v>2741</v>
       </c>
       <c r="I37" t="s">
         <v>4</v>
@@ -26135,28 +26141,28 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>2756</v>
+        <v>2758</v>
       </c>
       <c r="B38" t="s">
-        <v>2757</v>
+        <v>2759</v>
       </c>
       <c r="C38" t="s">
         <v>462</v>
       </c>
       <c r="D38" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E38" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F38" t="s">
-        <v>2742</v>
+        <v>2744</v>
       </c>
       <c r="G38" t="s">
-        <v>2758</v>
+        <v>2760</v>
       </c>
       <c r="H38" t="s">
-        <v>2738</v>
+        <v>2741</v>
       </c>
       <c r="I38" t="s">
         <v>4</v>
@@ -26170,28 +26176,28 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2759</v>
+        <v>2761</v>
       </c>
       <c r="B39" t="s">
-        <v>2760</v>
+        <v>2762</v>
       </c>
       <c r="C39" t="s">
         <v>462</v>
       </c>
       <c r="D39" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E39" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F39" t="s">
-        <v>2742</v>
+        <v>2744</v>
       </c>
       <c r="G39" t="s">
-        <v>2761</v>
+        <v>2763</v>
       </c>
       <c r="H39" t="s">
-        <v>2738</v>
+        <v>2741</v>
       </c>
       <c r="I39" t="s">
         <v>4</v>
@@ -26205,28 +26211,28 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2762</v>
+        <v>2764</v>
       </c>
       <c r="B40" t="s">
-        <v>2763</v>
+        <v>2765</v>
       </c>
       <c r="C40" t="s">
         <v>462</v>
       </c>
       <c r="D40" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E40" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F40" t="s">
-        <v>2742</v>
+        <v>2744</v>
       </c>
       <c r="G40" t="s">
-        <v>2764</v>
+        <v>2766</v>
       </c>
       <c r="H40" t="s">
-        <v>2738</v>
+        <v>2741</v>
       </c>
       <c r="I40" t="s">
         <v>4</v>
@@ -26240,28 +26246,28 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>2765</v>
+        <v>2767</v>
       </c>
       <c r="B41" t="s">
-        <v>2766</v>
+        <v>2768</v>
       </c>
       <c r="C41" t="s">
         <v>462</v>
       </c>
       <c r="D41" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E41" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F41" t="s">
-        <v>2742</v>
+        <v>2744</v>
       </c>
       <c r="G41" t="s">
-        <v>2767</v>
+        <v>2769</v>
       </c>
       <c r="H41" t="s">
-        <v>2738</v>
+        <v>2741</v>
       </c>
       <c r="I41" t="s">
         <v>4</v>
@@ -26275,28 +26281,28 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>2768</v>
+        <v>2770</v>
       </c>
       <c r="B42" t="s">
-        <v>2769</v>
+        <v>2771</v>
       </c>
       <c r="C42" t="s">
         <v>462</v>
       </c>
       <c r="D42" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E42" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F42" t="s">
-        <v>2742</v>
+        <v>2744</v>
       </c>
       <c r="G42" t="s">
-        <v>2770</v>
+        <v>2772</v>
       </c>
       <c r="H42" t="s">
-        <v>2738</v>
+        <v>2741</v>
       </c>
       <c r="I42" t="s">
         <v>4</v>
@@ -26305,33 +26311,33 @@
         <v>9</v>
       </c>
       <c r="K42" t="s">
-        <v>2739</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>2771</v>
+        <v>2773</v>
       </c>
       <c r="B43" t="s">
-        <v>2772</v>
+        <v>2774</v>
       </c>
       <c r="C43" t="s">
         <v>462</v>
       </c>
       <c r="D43" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E43" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F43" t="s">
-        <v>2773</v>
+        <v>2775</v>
       </c>
       <c r="G43" t="s">
-        <v>2774</v>
+        <v>2776</v>
       </c>
       <c r="H43" t="s">
-        <v>2738</v>
+        <v>2741</v>
       </c>
       <c r="I43" t="s">
         <v>4</v>
@@ -26340,33 +26346,33 @@
         <v>9</v>
       </c>
       <c r="K43" t="s">
-        <v>2739</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>2775</v>
+        <v>2777</v>
       </c>
       <c r="B44" t="s">
-        <v>2776</v>
+        <v>2778</v>
       </c>
       <c r="C44" t="s">
         <v>462</v>
       </c>
       <c r="D44" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E44" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F44" t="s">
-        <v>2742</v>
+        <v>2744</v>
       </c>
       <c r="G44" t="s">
-        <v>2777</v>
+        <v>2779</v>
       </c>
       <c r="H44" t="s">
-        <v>2738</v>
+        <v>2741</v>
       </c>
       <c r="I44" t="s">
         <v>4</v>
@@ -26375,33 +26381,33 @@
         <v>9</v>
       </c>
       <c r="K44" t="s">
-        <v>2739</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>2778</v>
+        <v>2780</v>
       </c>
       <c r="B45" t="s">
-        <v>2779</v>
+        <v>2781</v>
       </c>
       <c r="C45" t="s">
         <v>462</v>
       </c>
       <c r="D45" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E45" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="F45" t="s">
-        <v>2780</v>
+        <v>2782</v>
       </c>
       <c r="G45" t="s">
-        <v>2781</v>
+        <v>2783</v>
       </c>
       <c r="H45" t="s">
-        <v>2782</v>
+        <v>2784</v>
       </c>
       <c r="I45" t="s">
         <v>4</v>
@@ -26410,7 +26416,7 @@
         <v>9</v>
       </c>
       <c r="K45" t="s">
-        <v>2739</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -26418,7 +26424,7 @@
         <v>144</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>2783</v>
+        <v>2785</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>70</v>
@@ -26439,10 +26445,10 @@
         <v>70</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>2784</v>
+        <v>2786</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>2785</v>
+        <v>2787</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>148</v>
